--- a/examples/example_output/scores_1Hz.xlsx
+++ b/examples/example_output/scores_1Hz.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>0.06558874249458313</v>
+        <v>0.06558875739574432</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -517,7 +517,7 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <v>0.04702372476458549</v>
+        <v>0.047023706138134</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>0.05984292551875114</v>
+        <v>0.05984293669462204</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -569,7 +569,7 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>0.04196886345744133</v>
+        <v>0.04196885228157043</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -595,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="G6">
-        <v>0.02676481194794178</v>
+        <v>0.02676483057439327</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>18</v>
       </c>
       <c r="G7">
-        <v>0.05377430096268654</v>
+        <v>0.05377423763275146</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -647,7 +647,7 @@
         <v>21</v>
       </c>
       <c r="G8">
-        <v>0.03522386774420738</v>
+        <v>0.0352238267660141</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>24</v>
       </c>
       <c r="G9">
-        <v>0.03497651219367981</v>
+        <v>0.0349765419960022</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>27</v>
       </c>
       <c r="G10">
-        <v>0.0694047287106514</v>
+        <v>0.06940482556819916</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -725,7 +725,7 @@
         <v>30</v>
       </c>
       <c r="G11">
-        <v>0.1152019426226616</v>
+        <v>0.1152019947767258</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>33</v>
       </c>
       <c r="G12">
-        <v>0.0988016277551651</v>
+        <v>0.09880149364471436</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>36</v>
       </c>
       <c r="G13">
-        <v>0.04741423204541206</v>
+        <v>0.04741424322128296</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>39</v>
       </c>
       <c r="G14">
-        <v>0.05399538949131966</v>
+        <v>0.05399542674422264</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>42</v>
       </c>
       <c r="G15">
-        <v>0.05495421215891838</v>
+        <v>0.05495422706007957</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>45</v>
       </c>
       <c r="G16">
-        <v>0.02952717989683151</v>
+        <v>0.02952718734741211</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>48</v>
       </c>
       <c r="G17">
-        <v>0.04344293475151062</v>
+        <v>0.04344292357563972</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>51</v>
       </c>
       <c r="G18">
-        <v>0.05569244921207428</v>
+        <v>0.0556923970580101</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -933,7 +933,7 @@
         <v>54</v>
       </c>
       <c r="G19">
-        <v>0.04781657829880714</v>
+        <v>0.04781656339764595</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -959,7 +959,7 @@
         <v>57</v>
       </c>
       <c r="G20">
-        <v>0.06429806351661682</v>
+        <v>0.0642981231212616</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>60</v>
       </c>
       <c r="G21">
-        <v>0.08607229590415955</v>
+        <v>0.0860721617937088</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>63</v>
       </c>
       <c r="G22">
-        <v>0.07598603516817093</v>
+        <v>0.07598613947629929</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>66</v>
       </c>
       <c r="G23">
-        <v>0.04510330781340599</v>
+        <v>0.04510335251688957</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1063,7 +1063,7 @@
         <v>69</v>
       </c>
       <c r="G24">
-        <v>0.04024746641516685</v>
+        <v>0.04024744406342506</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1089,7 +1089,7 @@
         <v>72</v>
       </c>
       <c r="G25">
-        <v>0.0592171885073185</v>
+        <v>0.05921714752912521</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>75</v>
       </c>
       <c r="G26">
-        <v>0.05034182220697403</v>
+        <v>0.05034186691045761</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>78</v>
       </c>
       <c r="G27">
-        <v>0.09505794942378998</v>
+        <v>0.09505786001682281</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>81</v>
       </c>
       <c r="G28">
-        <v>0.04346940666437149</v>
+        <v>0.04346943646669388</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1193,7 +1193,7 @@
         <v>84</v>
       </c>
       <c r="G29">
-        <v>0.05391848087310791</v>
+        <v>0.05391846969723701</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>87</v>
       </c>
       <c r="G30">
-        <v>0.03199268504977226</v>
+        <v>0.03199270740151405</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1245,7 +1245,7 @@
         <v>90</v>
       </c>
       <c r="G31">
-        <v>0.02434511482715607</v>
+        <v>0.02434509806334972</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>93</v>
       </c>
       <c r="G32">
-        <v>0.06189408153295517</v>
+        <v>0.06189409643411636</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>96</v>
       </c>
       <c r="G33">
-        <v>0.04256702587008476</v>
+        <v>0.04256699606776237</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>99</v>
       </c>
       <c r="G34">
-        <v>0.08779525756835938</v>
+        <v>0.08779527246952057</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1349,7 +1349,7 @@
         <v>102</v>
       </c>
       <c r="G35">
-        <v>0.1023445725440979</v>
+        <v>0.1023445948958397</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>105</v>
       </c>
       <c r="G36">
-        <v>0.06311607360839844</v>
+        <v>0.06311605870723724</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>108</v>
       </c>
       <c r="G37">
-        <v>0.1035041213035583</v>
+        <v>0.1035041436553001</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v>111</v>
       </c>
       <c r="G38">
-        <v>0.08297614008188248</v>
+        <v>0.08297600597143173</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>123</v>
       </c>
       <c r="G42">
-        <v>0.05721937492489815</v>
+        <v>0.05721940100193024</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         <v>129</v>
       </c>
       <c r="G44">
-        <v>0.04560172185301781</v>
+        <v>0.04560176283121109</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>132</v>
       </c>
       <c r="G45">
-        <v>0.08128824830055237</v>
+        <v>0.0812881737947464</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>135</v>
       </c>
       <c r="G46">
-        <v>0.03137771785259247</v>
+        <v>0.03137768805027008</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>138</v>
       </c>
       <c r="G47">
-        <v>0.05109610036015511</v>
+        <v>0.05109605193138123</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>141</v>
       </c>
       <c r="G48">
-        <v>0.0202003363519907</v>
+        <v>0.020200340077281</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>144</v>
       </c>
       <c r="G49">
-        <v>0.02756345085799694</v>
+        <v>0.0275634303689003</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>147</v>
       </c>
       <c r="G50">
-        <v>0.03774332627654076</v>
+        <v>0.03774334862828255</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         <v>150</v>
       </c>
       <c r="G51">
-        <v>0.02243846841156483</v>
+        <v>0.02243843302130699</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>153</v>
       </c>
       <c r="G52">
-        <v>0.02054749429225922</v>
+        <v>0.02054748684167862</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>156</v>
       </c>
       <c r="G53">
-        <v>0.02902907133102417</v>
+        <v>0.02902905829250813</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>159</v>
       </c>
       <c r="G54">
-        <v>0.02275886200368404</v>
+        <v>0.0227588377892971</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>165</v>
       </c>
       <c r="G56">
-        <v>0.01557787321507931</v>
+        <v>0.0155778881162405</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>168</v>
       </c>
       <c r="G57">
-        <v>0.0225616879761219</v>
+        <v>0.02256171405315399</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         <v>171</v>
       </c>
       <c r="G58">
-        <v>0.0236325915902853</v>
+        <v>0.02363260835409164</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>174</v>
       </c>
       <c r="G59">
-        <v>0.01846378110349178</v>
+        <v>0.01846379227936268</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>177</v>
       </c>
       <c r="G60">
-        <v>0.007495521567761898</v>
+        <v>0.00749551085755229</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>180</v>
       </c>
       <c r="G61">
-        <v>0.02260527014732361</v>
+        <v>0.02260526455938816</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>183</v>
       </c>
       <c r="G62">
-        <v>0.03876600041985512</v>
+        <v>0.03876600787043571</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -2077,7 +2077,7 @@
         <v>186</v>
       </c>
       <c r="G63">
-        <v>0.03850150108337402</v>
+        <v>0.03850144892930984</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>189</v>
       </c>
       <c r="G64">
-        <v>0.05689607933163643</v>
+        <v>0.05689600110054016</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>192</v>
       </c>
       <c r="G65">
-        <v>0.02752827107906342</v>
+        <v>0.02752828225493431</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2155,7 +2155,7 @@
         <v>195</v>
       </c>
       <c r="G66">
-        <v>0.08208125829696655</v>
+        <v>0.08208127319812775</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         <v>198</v>
       </c>
       <c r="G67">
-        <v>0.02394268289208412</v>
+        <v>0.02394267544150352</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2207,7 +2207,7 @@
         <v>201</v>
       </c>
       <c r="G68">
-        <v>0.02315129712224007</v>
+        <v>0.02315131202340126</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>204</v>
       </c>
       <c r="G69">
-        <v>0.04223215579986572</v>
+        <v>0.04223213344812393</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>207</v>
       </c>
       <c r="G70">
-        <v>0.02147392556071281</v>
+        <v>0.02147389575839043</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>210</v>
       </c>
       <c r="G71">
-        <v>0.04175989702343941</v>
+        <v>0.0417599156498909</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>213</v>
       </c>
       <c r="G72">
-        <v>0.01325742248445749</v>
+        <v>0.01325740944594145</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>216</v>
       </c>
       <c r="G73">
-        <v>0.01288431044667959</v>
+        <v>0.01288431603461504</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -2363,7 +2363,7 @@
         <v>219</v>
       </c>
       <c r="G74">
-        <v>0.02610877528786659</v>
+        <v>0.02610878273844719</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -2389,7 +2389,7 @@
         <v>222</v>
       </c>
       <c r="G75">
-        <v>0.02123190835118294</v>
+        <v>0.02123189158737659</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -2415,7 +2415,7 @@
         <v>225</v>
       </c>
       <c r="G76">
-        <v>0.01472072303295135</v>
+        <v>0.01472073700278997</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         <v>228</v>
       </c>
       <c r="G77">
-        <v>0.02052216790616512</v>
+        <v>0.02052219957113266</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -2467,7 +2467,7 @@
         <v>231</v>
       </c>
       <c r="G78">
-        <v>0.01453312207013369</v>
+        <v>0.01453310903161764</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2493,7 +2493,7 @@
         <v>234</v>
       </c>
       <c r="G79">
-        <v>0.01699922606348991</v>
+        <v>0.01699921861290932</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         <v>237</v>
       </c>
       <c r="G80">
-        <v>0.04491019248962402</v>
+        <v>0.04491022229194641</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2545,7 +2545,7 @@
         <v>240</v>
       </c>
       <c r="G81">
-        <v>0.0335996076464653</v>
+        <v>0.03359955921769142</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2571,7 +2571,7 @@
         <v>243</v>
       </c>
       <c r="G82">
-        <v>0.03258050233125687</v>
+        <v>0.03258054330945015</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2597,7 +2597,7 @@
         <v>246</v>
       </c>
       <c r="G83">
-        <v>0.02769523300230503</v>
+        <v>0.02769521251320839</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2623,7 +2623,7 @@
         <v>249</v>
       </c>
       <c r="G84">
-        <v>0.02859092690050602</v>
+        <v>0.02859095297753811</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2649,7 +2649,7 @@
         <v>252</v>
       </c>
       <c r="G85">
-        <v>0.05501343309879303</v>
+        <v>0.05501341074705124</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>255</v>
       </c>
       <c r="G86">
-        <v>0.04221328720450401</v>
+        <v>0.04221333563327789</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2701,7 +2701,7 @@
         <v>258</v>
       </c>
       <c r="G87">
-        <v>0.0529041551053524</v>
+        <v>0.05290414392948151</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -2727,7 +2727,7 @@
         <v>261</v>
       </c>
       <c r="G88">
-        <v>0.01722502335906029</v>
+        <v>0.01722501590847969</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>264</v>
       </c>
       <c r="G89">
-        <v>0.0285016056150198</v>
+        <v>0.0285015981644392</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -2779,7 +2779,7 @@
         <v>267</v>
       </c>
       <c r="G90">
-        <v>0.009062150493264198</v>
+        <v>0.009062145836651325</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -2805,7 +2805,7 @@
         <v>270</v>
       </c>
       <c r="G91">
-        <v>0.01382532622665167</v>
+        <v>0.01382535882294178</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -2831,7 +2831,7 @@
         <v>273</v>
       </c>
       <c r="G92">
-        <v>0.02349416166543961</v>
+        <v>0.02349419891834259</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -2857,7 +2857,7 @@
         <v>276</v>
       </c>
       <c r="G93">
-        <v>0.02254969254136086</v>
+        <v>0.0225497130304575</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -2883,7 +2883,7 @@
         <v>279</v>
       </c>
       <c r="G94">
-        <v>0.02189739234745502</v>
+        <v>0.02189742214977741</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -2909,7 +2909,7 @@
         <v>282</v>
       </c>
       <c r="G95">
-        <v>0.01082197669893503</v>
+        <v>0.01082197111099958</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -2961,7 +2961,7 @@
         <v>288</v>
       </c>
       <c r="G97">
-        <v>0.0238250307738781</v>
+        <v>0.02382505312561989</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>291</v>
       </c>
       <c r="G98">
-        <v>0.03201436623930931</v>
+        <v>0.0320143811404705</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3065,7 +3065,7 @@
         <v>300</v>
       </c>
       <c r="G101">
-        <v>0.02559351176023483</v>
+        <v>0.02559353411197662</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3091,7 +3091,7 @@
         <v>303</v>
       </c>
       <c r="G102">
-        <v>0.02051318623125553</v>
+        <v>0.02051318809390068</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3117,7 +3117,7 @@
         <v>306</v>
       </c>
       <c r="G103">
-        <v>0.03754046186804771</v>
+        <v>0.0375404916703701</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3143,7 +3143,7 @@
         <v>309</v>
       </c>
       <c r="G104">
-        <v>0.04078470170497894</v>
+        <v>0.04078463837504387</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3221,7 +3221,7 @@
         <v>318</v>
       </c>
       <c r="G107">
-        <v>0.02056950703263283</v>
+        <v>0.02056949213147163</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -3273,7 +3273,7 @@
         <v>324</v>
       </c>
       <c r="G109">
-        <v>0.01704959012567997</v>
+        <v>0.01704958267509937</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -3299,7 +3299,7 @@
         <v>327</v>
       </c>
       <c r="G110">
-        <v>0.02095871791243553</v>
+        <v>0.02095873840153217</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -3351,7 +3351,7 @@
         <v>333</v>
       </c>
       <c r="G112">
-        <v>0.01501393225044012</v>
+        <v>0.01501394622027874</v>
       </c>
       <c r="H112">
         <v>1</v>
@@ -3377,7 +3377,7 @@
         <v>336</v>
       </c>
       <c r="G113">
-        <v>0.01438614912331104</v>
+        <v>0.01438613515347242</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -3403,7 +3403,7 @@
         <v>339</v>
       </c>
       <c r="G114">
-        <v>0.01892751269042492</v>
+        <v>0.01892751455307007</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -3429,7 +3429,7 @@
         <v>342</v>
       </c>
       <c r="G115">
-        <v>0.03537286818027496</v>
+        <v>0.03537286072969437</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         <v>345</v>
       </c>
       <c r="G116">
-        <v>0.02569855004549026</v>
+        <v>0.02569853141903877</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -3481,7 +3481,7 @@
         <v>348</v>
       </c>
       <c r="G117">
-        <v>0.01482095289975405</v>
+        <v>0.01482096780091524</v>
       </c>
       <c r="H117">
         <v>1</v>
@@ -3507,7 +3507,7 @@
         <v>351</v>
       </c>
       <c r="G118">
-        <v>0.02750507183372974</v>
+        <v>0.02750508487224579</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -3533,7 +3533,7 @@
         <v>354</v>
       </c>
       <c r="G119">
-        <v>0.02786325477063656</v>
+        <v>0.02786329202353954</v>
       </c>
       <c r="H119">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         <v>357</v>
       </c>
       <c r="G120">
-        <v>0.04726274684071541</v>
+        <v>0.04726271703839302</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -3585,7 +3585,7 @@
         <v>360</v>
       </c>
       <c r="G121">
-        <v>0.03336017578840256</v>
+        <v>0.03336018323898315</v>
       </c>
       <c r="H121">
         <v>1</v>
@@ -3611,7 +3611,7 @@
         <v>363</v>
       </c>
       <c r="G122">
-        <v>0.02004683949053288</v>
+        <v>0.02004683390259743</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -3637,7 +3637,7 @@
         <v>366</v>
       </c>
       <c r="G123">
-        <v>0.02578539401292801</v>
+        <v>0.02578539960086346</v>
       </c>
       <c r="H123">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>369</v>
       </c>
       <c r="G124">
-        <v>0.0237040501087904</v>
+        <v>0.02370403334498405</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -3689,7 +3689,7 @@
         <v>372</v>
       </c>
       <c r="G125">
-        <v>0.02965923584997654</v>
+        <v>0.0296592153608799</v>
       </c>
       <c r="H125">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>375</v>
       </c>
       <c r="G126">
-        <v>0.04300208017230034</v>
+        <v>0.04300213232636452</v>
       </c>
       <c r="H126">
         <v>1</v>
@@ -3741,7 +3741,7 @@
         <v>378</v>
       </c>
       <c r="G127">
-        <v>0.03968352451920509</v>
+        <v>0.03968352079391479</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -3767,7 +3767,7 @@
         <v>381</v>
       </c>
       <c r="G128">
-        <v>0.02913433313369751</v>
+        <v>0.02913431264460087</v>
       </c>
       <c r="H128">
         <v>1</v>
@@ -3793,7 +3793,7 @@
         <v>384</v>
       </c>
       <c r="G129">
-        <v>0.01155733317136765</v>
+        <v>0.01155732199549675</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -3819,7 +3819,7 @@
         <v>387</v>
       </c>
       <c r="G130">
-        <v>0.02189318463206291</v>
+        <v>0.02189313620328903</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -3845,7 +3845,7 @@
         <v>390</v>
       </c>
       <c r="G131">
-        <v>0.0267366748303175</v>
+        <v>0.02673669345676899</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         <v>393</v>
       </c>
       <c r="G132">
-        <v>0.0280015841126442</v>
+        <v>0.02800159715116024</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -3897,7 +3897,7 @@
         <v>396</v>
       </c>
       <c r="G133">
-        <v>0.02758943662047386</v>
+        <v>0.02758944965898991</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -3923,7 +3923,7 @@
         <v>399</v>
       </c>
       <c r="G134">
-        <v>0.02508834563195705</v>
+        <v>0.02508831024169922</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -3949,7 +3949,7 @@
         <v>402</v>
       </c>
       <c r="G135">
-        <v>0.0874347910284996</v>
+        <v>0.08743473142385483</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -3975,7 +3975,7 @@
         <v>405</v>
       </c>
       <c r="G136">
-        <v>0.02135919407010078</v>
+        <v>0.02135918289422989</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -4001,7 +4001,7 @@
         <v>408</v>
       </c>
       <c r="G137">
-        <v>0.01503766234964132</v>
+        <v>0.01503767725080252</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -4027,7 +4027,7 @@
         <v>411</v>
       </c>
       <c r="G138">
-        <v>0.03110033273696899</v>
+        <v>0.03110036253929138</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -4053,7 +4053,7 @@
         <v>414</v>
       </c>
       <c r="G139">
-        <v>0.02418014034628868</v>
+        <v>0.02418014593422413</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -4079,7 +4079,7 @@
         <v>3</v>
       </c>
       <c r="G140">
-        <v>0.1040638014674187</v>
+        <v>0.1040637791156769</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="G141">
-        <v>0.09555720537900925</v>
+        <v>0.09555716067552567</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -4131,7 +4131,7 @@
         <v>9</v>
       </c>
       <c r="G142">
-        <v>0.03974515199661255</v>
+        <v>0.03974518179893494</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -4157,7 +4157,7 @@
         <v>12</v>
       </c>
       <c r="G143">
-        <v>0.07523269951343536</v>
+        <v>0.0752326101064682</v>
       </c>
       <c r="H143">
         <v>1</v>
@@ -4183,7 +4183,7 @@
         <v>15</v>
       </c>
       <c r="G144">
-        <v>0.06628566235303879</v>
+        <v>0.06628571450710297</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -4209,7 +4209,7 @@
         <v>18</v>
       </c>
       <c r="G145">
-        <v>0.07984476536512375</v>
+        <v>0.07984474301338196</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -4235,7 +4235,7 @@
         <v>21</v>
       </c>
       <c r="G146">
-        <v>0.1109033897519112</v>
+        <v>0.1109034046530724</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -4261,7 +4261,7 @@
         <v>24</v>
       </c>
       <c r="G147">
-        <v>0.04878461360931396</v>
+        <v>0.04878462478518486</v>
       </c>
       <c r="H147">
         <v>1</v>
@@ -4287,7 +4287,7 @@
         <v>27</v>
       </c>
       <c r="G148">
-        <v>0.07530995458364487</v>
+        <v>0.07531000673770905</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -4313,7 +4313,7 @@
         <v>30</v>
       </c>
       <c r="G149">
-        <v>0.08476787060499191</v>
+        <v>0.08476794511079788</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -4339,7 +4339,7 @@
         <v>33</v>
       </c>
       <c r="G150">
-        <v>0.06674117594957352</v>
+        <v>0.06674114614725113</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -4365,7 +4365,7 @@
         <v>36</v>
       </c>
       <c r="G151">
-        <v>0.1151515915989876</v>
+        <v>0.1151515394449234</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -4391,7 +4391,7 @@
         <v>39</v>
       </c>
       <c r="G152">
-        <v>0.1059208661317825</v>
+        <v>0.1059208959341049</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>42</v>
       </c>
       <c r="G153">
-        <v>0.1239887848496437</v>
+        <v>0.1239887028932571</v>
       </c>
       <c r="H153">
         <v>1</v>
@@ -4443,7 +4443,7 @@
         <v>45</v>
       </c>
       <c r="G154">
-        <v>0.05208753421902657</v>
+        <v>0.05208757147192955</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -4469,7 +4469,7 @@
         <v>48</v>
       </c>
       <c r="G155">
-        <v>0.05026783794164658</v>
+        <v>0.05026781558990479</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -4495,7 +4495,7 @@
         <v>51</v>
       </c>
       <c r="G156">
-        <v>0.08106322586536407</v>
+        <v>0.08106335252523422</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -4521,7 +4521,7 @@
         <v>54</v>
       </c>
       <c r="G157">
-        <v>0.05980586260557175</v>
+        <v>0.05980575084686279</v>
       </c>
       <c r="H157">
         <v>1</v>
@@ -4573,7 +4573,7 @@
         <v>60</v>
       </c>
       <c r="G159">
-        <v>0.1244068592786789</v>
+        <v>0.1244067028164864</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -4599,7 +4599,7 @@
         <v>63</v>
       </c>
       <c r="G160">
-        <v>0.08994641155004501</v>
+        <v>0.08994637429714203</v>
       </c>
       <c r="H160">
         <v>1</v>
@@ -4651,7 +4651,7 @@
         <v>69</v>
       </c>
       <c r="G162">
-        <v>0.05476316809654236</v>
+        <v>0.05476320534944534</v>
       </c>
       <c r="H162">
         <v>1</v>
@@ -4677,7 +4677,7 @@
         <v>72</v>
       </c>
       <c r="G163">
-        <v>0.09752239286899567</v>
+        <v>0.09752237051725388</v>
       </c>
       <c r="H163">
         <v>1</v>
@@ -4703,7 +4703,7 @@
         <v>75</v>
       </c>
       <c r="G164">
-        <v>0.1185721158981323</v>
+        <v>0.118572011590004</v>
       </c>
       <c r="H164">
         <v>1</v>
@@ -4729,7 +4729,7 @@
         <v>78</v>
       </c>
       <c r="G165">
-        <v>0.1558298021554947</v>
+        <v>0.1558297872543335</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -4755,7 +4755,7 @@
         <v>81</v>
       </c>
       <c r="G166">
-        <v>0.05088484659790993</v>
+        <v>0.05088488385081291</v>
       </c>
       <c r="H166">
         <v>1</v>
@@ -4807,7 +4807,7 @@
         <v>87</v>
       </c>
       <c r="G168">
-        <v>0.07478943467140198</v>
+        <v>0.07478941231966019</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -4833,7 +4833,7 @@
         <v>90</v>
       </c>
       <c r="G169">
-        <v>0.07162440568208694</v>
+        <v>0.07162442803382874</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -4885,7 +4885,7 @@
         <v>96</v>
       </c>
       <c r="G171">
-        <v>0.07498066872358322</v>
+        <v>0.07498063147068024</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -4911,7 +4911,7 @@
         <v>99</v>
       </c>
       <c r="G172">
-        <v>0.05357460677623749</v>
+        <v>0.0535745732486248</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -4937,7 +4937,7 @@
         <v>102</v>
       </c>
       <c r="G173">
-        <v>0.04715191200375557</v>
+        <v>0.04715185612440109</v>
       </c>
       <c r="H173">
         <v>1</v>
@@ -4963,7 +4963,7 @@
         <v>105</v>
       </c>
       <c r="G174">
-        <v>0.04949158430099487</v>
+        <v>0.04949161410331726</v>
       </c>
       <c r="H174">
         <v>1</v>
@@ -4989,7 +4989,7 @@
         <v>108</v>
       </c>
       <c r="G175">
-        <v>0.03249185159802437</v>
+        <v>0.03249183297157288</v>
       </c>
       <c r="H175">
         <v>1</v>
@@ -5015,7 +5015,7 @@
         <v>111</v>
       </c>
       <c r="G176">
-        <v>0.0518486425280571</v>
+        <v>0.05184859782457352</v>
       </c>
       <c r="H176">
         <v>1</v>
@@ -5041,7 +5041,7 @@
         <v>114</v>
       </c>
       <c r="G177">
-        <v>0.06280724704265594</v>
+        <v>0.06280723214149475</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -5067,7 +5067,7 @@
         <v>117</v>
       </c>
       <c r="G178">
-        <v>0.05330724269151688</v>
+        <v>0.05330720543861389</v>
       </c>
       <c r="H178">
         <v>1</v>
@@ -5093,7 +5093,7 @@
         <v>120</v>
       </c>
       <c r="G179">
-        <v>0.06696071475744247</v>
+        <v>0.06696072965860367</v>
       </c>
       <c r="H179">
         <v>1</v>
@@ -5119,7 +5119,7 @@
         <v>123</v>
       </c>
       <c r="G180">
-        <v>0.04007459431886673</v>
+        <v>0.04007462412118912</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         <v>126</v>
       </c>
       <c r="G181">
-        <v>0.04101533070206642</v>
+        <v>0.04101531952619553</v>
       </c>
       <c r="H181">
         <v>1</v>
@@ -5171,7 +5171,7 @@
         <v>129</v>
       </c>
       <c r="G182">
-        <v>0.06138283386826515</v>
+        <v>0.06138286367058754</v>
       </c>
       <c r="H182">
         <v>1</v>
@@ -5223,7 +5223,7 @@
         <v>135</v>
       </c>
       <c r="G184">
-        <v>0.03298868611454964</v>
+        <v>0.03298866003751755</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -5301,7 +5301,7 @@
         <v>144</v>
       </c>
       <c r="G187">
-        <v>0.03645997494459152</v>
+        <v>0.03645994514226913</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -5327,7 +5327,7 @@
         <v>147</v>
       </c>
       <c r="G188">
-        <v>0.06867256015539169</v>
+        <v>0.06867250055074692</v>
       </c>
       <c r="H188">
         <v>0</v>
@@ -5379,7 +5379,7 @@
         <v>153</v>
       </c>
       <c r="G190">
-        <v>0.1206632703542709</v>
+        <v>0.1206633672118187</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -5405,7 +5405,7 @@
         <v>156</v>
       </c>
       <c r="G191">
-        <v>0.08305691927671432</v>
+        <v>0.08305695652961731</v>
       </c>
       <c r="H191">
         <v>0</v>
@@ -5457,7 +5457,7 @@
         <v>162</v>
       </c>
       <c r="G193">
-        <v>0.06074934080243111</v>
+        <v>0.0607493557035923</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -5509,7 +5509,7 @@
         <v>168</v>
       </c>
       <c r="G195">
-        <v>0.05579156801104546</v>
+        <v>0.05579159036278725</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -5535,7 +5535,7 @@
         <v>171</v>
       </c>
       <c r="G196">
-        <v>0.06160104274749756</v>
+        <v>0.06160103157162666</v>
       </c>
       <c r="H196">
         <v>0</v>
@@ -5561,7 +5561,7 @@
         <v>174</v>
       </c>
       <c r="G197">
-        <v>0.07298024743795395</v>
+        <v>0.07298022508621216</v>
       </c>
       <c r="H197">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>177</v>
       </c>
       <c r="G198">
-        <v>0.05342917889356613</v>
+        <v>0.05342913046479225</v>
       </c>
       <c r="H198">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>180</v>
       </c>
       <c r="G199">
-        <v>0.07241453230381012</v>
+        <v>0.07241450250148773</v>
       </c>
       <c r="H199">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         <v>183</v>
       </c>
       <c r="G200">
-        <v>0.03454460948705673</v>
+        <v>0.03454467281699181</v>
       </c>
       <c r="H200">
         <v>0</v>
@@ -5665,7 +5665,7 @@
         <v>186</v>
       </c>
       <c r="G201">
-        <v>0.04202350601553917</v>
+        <v>0.04202349856495857</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>189</v>
       </c>
       <c r="G202">
-        <v>0.06497582793235779</v>
+        <v>0.06497588008642197</v>
       </c>
       <c r="H202">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>192</v>
       </c>
       <c r="G203">
-        <v>0.06484299898147583</v>
+        <v>0.0648430734872818</v>
       </c>
       <c r="H203">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         <v>195</v>
       </c>
       <c r="G204">
-        <v>0.05630448833107948</v>
+        <v>0.05630449950695038</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>198</v>
       </c>
       <c r="G205">
-        <v>0.06430919468402863</v>
+        <v>0.06430917978286743</v>
       </c>
       <c r="H205">
         <v>1</v>
@@ -5795,7 +5795,7 @@
         <v>201</v>
       </c>
       <c r="G206">
-        <v>0.07863073796033859</v>
+        <v>0.07863066345453262</v>
       </c>
       <c r="H206">
         <v>1</v>
@@ -5821,7 +5821,7 @@
         <v>204</v>
       </c>
       <c r="G207">
-        <v>0.07834863662719727</v>
+        <v>0.07834868878126144</v>
       </c>
       <c r="H207">
         <v>1</v>
@@ -5847,7 +5847,7 @@
         <v>207</v>
       </c>
       <c r="G208">
-        <v>0.05261446535587311</v>
+        <v>0.05261436849832535</v>
       </c>
       <c r="H208">
         <v>1</v>
@@ -5873,7 +5873,7 @@
         <v>210</v>
       </c>
       <c r="G209">
-        <v>0.0497123971581459</v>
+        <v>0.0497124083340168</v>
       </c>
       <c r="H209">
         <v>1</v>
@@ -5899,7 +5899,7 @@
         <v>213</v>
       </c>
       <c r="G210">
-        <v>0.05176004394888878</v>
+        <v>0.0517599955201149</v>
       </c>
       <c r="H210">
         <v>1</v>
@@ -5925,7 +5925,7 @@
         <v>216</v>
       </c>
       <c r="G211">
-        <v>0.0474826768040657</v>
+        <v>0.04748265445232391</v>
       </c>
       <c r="H211">
         <v>1</v>
@@ -5951,7 +5951,7 @@
         <v>219</v>
       </c>
       <c r="G212">
-        <v>0.03938274830579758</v>
+        <v>0.03938271477818489</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -5977,7 +5977,7 @@
         <v>222</v>
       </c>
       <c r="G213">
-        <v>0.07980828732252121</v>
+        <v>0.07980836182832718</v>
       </c>
       <c r="H213">
         <v>1</v>
@@ -6029,7 +6029,7 @@
         <v>228</v>
       </c>
       <c r="G215">
-        <v>0.06710325181484222</v>
+        <v>0.06710320711135864</v>
       </c>
       <c r="H215">
         <v>1</v>
@@ -6055,7 +6055,7 @@
         <v>231</v>
       </c>
       <c r="G216">
-        <v>0.09059585630893707</v>
+        <v>0.09059595316648483</v>
       </c>
       <c r="H216">
         <v>1</v>
@@ -6081,7 +6081,7 @@
         <v>234</v>
       </c>
       <c r="G217">
-        <v>0.07352763414382935</v>
+        <v>0.07352758944034576</v>
       </c>
       <c r="H217">
         <v>1</v>
@@ -6107,7 +6107,7 @@
         <v>237</v>
       </c>
       <c r="G218">
-        <v>0.1154907196760178</v>
+        <v>0.1154907718300819</v>
       </c>
       <c r="H218">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         <v>240</v>
       </c>
       <c r="G219">
-        <v>0.06675051897764206</v>
+        <v>0.06675050407648087</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -6159,7 +6159,7 @@
         <v>243</v>
       </c>
       <c r="G220">
-        <v>0.04579325020313263</v>
+        <v>0.04579319432377815</v>
       </c>
       <c r="H220">
         <v>1</v>
@@ -6211,7 +6211,7 @@
         <v>249</v>
       </c>
       <c r="G222">
-        <v>0.0530909076333046</v>
+        <v>0.05309087038040161</v>
       </c>
       <c r="H222">
         <v>1</v>
@@ -6263,7 +6263,7 @@
         <v>255</v>
       </c>
       <c r="G224">
-        <v>0.08712980151176453</v>
+        <v>0.08712988346815109</v>
       </c>
       <c r="H224">
         <v>1</v>
@@ -6315,7 +6315,7 @@
         <v>261</v>
       </c>
       <c r="G226">
-        <v>0.1423162519931793</v>
+        <v>0.1423162221908569</v>
       </c>
       <c r="H226">
         <v>1</v>
@@ -6341,7 +6341,7 @@
         <v>264</v>
       </c>
       <c r="G227">
-        <v>0.07425256073474884</v>
+        <v>0.07425252348184586</v>
       </c>
       <c r="H227">
         <v>1</v>
@@ -6367,7 +6367,7 @@
         <v>267</v>
       </c>
       <c r="G228">
-        <v>0.03772000595927238</v>
+        <v>0.03771999105811119</v>
       </c>
       <c r="H228">
         <v>1</v>
@@ -6393,7 +6393,7 @@
         <v>270</v>
       </c>
       <c r="G229">
-        <v>0.04187063872814178</v>
+        <v>0.04187065735459328</v>
       </c>
       <c r="H229">
         <v>1</v>
@@ -6419,7 +6419,7 @@
         <v>273</v>
       </c>
       <c r="G230">
-        <v>0.0711047425866127</v>
+        <v>0.07110471278429031</v>
       </c>
       <c r="H230">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>279</v>
       </c>
       <c r="G232">
-        <v>0.05472143366932869</v>
+        <v>0.05472148582339287</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -6497,7 +6497,7 @@
         <v>282</v>
       </c>
       <c r="G233">
-        <v>0.08853436261415482</v>
+        <v>0.08853438496589661</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>285</v>
       </c>
       <c r="G234">
-        <v>0.06669893860816956</v>
+        <v>0.06669895350933075</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -6549,7 +6549,7 @@
         <v>288</v>
       </c>
       <c r="G235">
-        <v>0.09128442406654358</v>
+        <v>0.09128444641828537</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>291</v>
       </c>
       <c r="G236">
-        <v>0.08897808194160461</v>
+        <v>0.08897810429334641</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -6653,7 +6653,7 @@
         <v>300</v>
       </c>
       <c r="G239">
-        <v>0.1347686499357224</v>
+        <v>0.1347688436508179</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -6679,7 +6679,7 @@
         <v>303</v>
       </c>
       <c r="G240">
-        <v>0.1067019701004028</v>
+        <v>0.106701947748661</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>306</v>
       </c>
       <c r="G241">
-        <v>0.08924489468336105</v>
+        <v>0.08924490958452225</v>
       </c>
       <c r="H241">
         <v>0</v>
@@ -6731,7 +6731,7 @@
         <v>309</v>
       </c>
       <c r="G242">
-        <v>0.1007561236619949</v>
+        <v>0.1007561460137367</v>
       </c>
       <c r="H242">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>312</v>
       </c>
       <c r="G243">
-        <v>0.08895213156938553</v>
+        <v>0.08895210921764374</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -6783,7 +6783,7 @@
         <v>315</v>
       </c>
       <c r="G244">
-        <v>0.07958044856786728</v>
+        <v>0.07958047091960907</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>318</v>
       </c>
       <c r="G245">
-        <v>0.09185697138309479</v>
+        <v>0.09185692667961121</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -6835,7 +6835,7 @@
         <v>321</v>
       </c>
       <c r="G246">
-        <v>0.05033636465668678</v>
+        <v>0.0503363199532032</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -6913,7 +6913,7 @@
         <v>330</v>
       </c>
       <c r="G249">
-        <v>0.1258102655410767</v>
+        <v>0.1258101463317871</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         <v>333</v>
       </c>
       <c r="G250">
-        <v>0.07266535609960556</v>
+        <v>0.07266540080308914</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -6965,7 +6965,7 @@
         <v>336</v>
       </c>
       <c r="G251">
-        <v>0.05920469015836716</v>
+        <v>0.05920471996068954</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>339</v>
       </c>
       <c r="G252">
-        <v>0.08142703771591187</v>
+        <v>0.08142691850662231</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>342</v>
       </c>
       <c r="G253">
-        <v>0.1257413327693939</v>
+        <v>0.1257414221763611</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>345</v>
       </c>
       <c r="G254">
-        <v>0.1221026033163071</v>
+        <v>0.122102789580822</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>351</v>
       </c>
       <c r="G256">
-        <v>0.08866559714078903</v>
+        <v>0.08866551518440247</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -7121,7 +7121,7 @@
         <v>354</v>
       </c>
       <c r="G257">
-        <v>0.1201314777135849</v>
+        <v>0.1201314553618431</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>357</v>
       </c>
       <c r="G258">
-        <v>0.06263953447341919</v>
+        <v>0.0626395046710968</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>366</v>
       </c>
       <c r="G261">
-        <v>0.05641523376107216</v>
+        <v>0.05641530826687813</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>369</v>
       </c>
       <c r="G262">
-        <v>0.04701802134513855</v>
+        <v>0.04701795428991318</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>372</v>
       </c>
       <c r="G263">
-        <v>0.06697807461023331</v>
+        <v>0.06697811186313629</v>
       </c>
       <c r="H263">
         <v>0</v>
@@ -7303,7 +7303,7 @@
         <v>375</v>
       </c>
       <c r="G264">
-        <v>0.08694564551115036</v>
+        <v>0.08694566786289215</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>378</v>
       </c>
       <c r="G265">
-        <v>0.06436047703027725</v>
+        <v>0.06436046212911606</v>
       </c>
       <c r="H265">
         <v>0</v>
@@ -7355,7 +7355,7 @@
         <v>381</v>
       </c>
       <c r="G266">
-        <v>0.1049710214138031</v>
+        <v>0.1049709767103195</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>384</v>
       </c>
       <c r="G267">
-        <v>0.0508294478058815</v>
+        <v>0.05082948133349419</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>387</v>
       </c>
       <c r="G268">
-        <v>0.04522044956684113</v>
+        <v>0.04522048309445381</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -7433,7 +7433,7 @@
         <v>390</v>
       </c>
       <c r="G269">
-        <v>0.0469166524708271</v>
+        <v>0.04691659286618233</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -7485,7 +7485,7 @@
         <v>396</v>
       </c>
       <c r="G271">
-        <v>0.1117629483342171</v>
+        <v>0.1117627993226051</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -7537,7 +7537,7 @@
         <v>402</v>
       </c>
       <c r="G273">
-        <v>0.04771754890680313</v>
+        <v>0.04771752282977104</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -7563,7 +7563,7 @@
         <v>405</v>
       </c>
       <c r="G274">
-        <v>0.0629340335726738</v>
+        <v>0.06293408572673798</v>
       </c>
       <c r="H274">
         <v>0</v>
@@ -7641,7 +7641,7 @@
         <v>414</v>
       </c>
       <c r="G277">
-        <v>0.05601324886083603</v>
+        <v>0.05601326376199722</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -7803,7 +7803,7 @@
         <v>21</v>
       </c>
       <c r="F2">
-        <v>0.03797529637813568</v>
+        <v>0.03797530382871628</v>
       </c>
       <c r="G2">
         <v>0.2088235294117647</v>
@@ -7826,7 +7826,7 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.07340523600578308</v>
+        <v>0.07340522855520248</v>
       </c>
       <c r="G3">
         <v>0.4595673177903802</v>
